--- a/reports/pdf_change_20260713.xlsx
+++ b/reports/pdf_change_20260713.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -985,371 +985,387 @@
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>63879200</v>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>6.95%→7.17%</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>3,141→3,229</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>-95693000</v>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>3.66%→3.38%</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>163→150</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>32831250</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>0.55%→0.66%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>83→98</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>-147900000</v>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>3.30%→2.86%</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>88→76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>30217500</v>
+        <v>63879200</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>0.64%→0.73%</t>
+          <t>6.95%→7.17%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>69→79</t>
+          <t>3,141→3,229</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-64685000</v>
+        <v>-95693000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.65%</t>
+          <t>3.66%→3.38%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>72→67</t>
+          <t>163→150</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>17671500</v>
+        <v>32831250</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2.70%→2.76%</t>
+          <t>0.55%→0.66%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>451→460</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-147900000</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>3.30%→2.86%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>88→76</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>30217500</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>0.64%→0.73%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>69→79</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-64685000</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>2.84%→2.65%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>72→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>17671500</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2.70%→2.76%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>451→460</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B32" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="11" t="n">
+      <c r="C32" s="11" t="n">
         <v>36618000</v>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>0.91%→1.03%</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>49→55</t>
         </is>
       </c>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="20" t="n"/>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="20" t="n"/>
-      <c r="K35" s="20" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="20" t="n"/>
+      <c r="J37" s="20" t="n"/>
+      <c r="K37" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A32:K32"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>

--- a/reports/pdf_change_20260713.xlsx
+++ b/reports/pdf_change_20260713.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 9종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 9종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>531521100</v>
+        <v>524700000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-17</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-536434150</v>
+        <v>-529550000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>554070480</v>
+        <v>546960000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-11</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-909268800</v>
+        <v>-897600000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>469069650</v>
+        <v>463050000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-9</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-398412900</v>
+        <v>-393300000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1447374400</v>
+        <v>1428800000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>485632200</v>
+        <v>479400000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>992841300</v>
+        <v>980100000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>965794200</v>
+        <v>953400000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>466790400</v>
+        <v>460800000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>421914500</v>
+        <v>416500000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -987,7 +987,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1011,7 +1011,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1035,7 +1035,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 5종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1131,11 +1131,11 @@
         <v>88</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>63879200</v>
+        <v>66796400</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>6.95%→7.17%</t>
+          <t>6.58%→6.80%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1152,11 +1152,11 @@
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-95693000</v>
+        <v>-114257000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.38%</t>
+          <t>3.95%→3.66%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1175,11 +1175,11 @@
         <v>15</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>32831250</v>
+        <v>39716250</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>0.55%→0.66%</t>
+          <t>0.61%→0.72%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1196,11 +1196,11 @@
         <v>-12</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-147900000</v>
+        <v>-181254000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>3.30%→2.86%</t>
+          <t>3.67%→3.18%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1219,11 +1219,11 @@
         <v>10</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>30217500</v>
+        <v>31960000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0.64%→0.73%</t>
+          <t>0.61%→0.70%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1240,11 +1240,11 @@
         <v>-5</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-64685000</v>
+        <v>-80495000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>2.84%→2.65%</t>
+          <t>3.20%→2.99%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1263,11 +1263,11 @@
         <v>9</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>17671500</v>
+        <v>18819000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>2.70%→2.76%</t>
+          <t>2.60%→2.67%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1291,11 +1291,11 @@
         <v>6</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>36618000</v>
+        <v>39168000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.03%</t>
+          <t>0.88%→1.00%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>

--- a/reports/pdf_change_20260713.xlsx
+++ b/reports/pdf_change_20260713.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 9종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억   ·   현금 60억(1.2%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 9종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -963,7 +963,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억   ·   현금 19억(0.4%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -987,7 +987,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 27억(0.9%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1011,7 +1011,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 27억(1.1%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1035,7 +1035,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 5종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 2억(100.0%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1312,7 +1312,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 9억(1.6%)      당일 2026-07-13  vs  전영업일 2026-07-10      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
